--- a/salidas/2026-10-18/ficha_datos_2026-10-18.xlsx
+++ b/salidas/2026-10-18/ficha_datos_2026-10-18.xlsx
@@ -1108,7 +1108,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>moviles</t>
+          <t>sujeta</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1124,7 +1124,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>sujeta</t>
+          <t>moviles</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1619,7 +1619,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>holder</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1635,7 +1635,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>holder</t>
+          <t>car</t>
         </is>
       </c>
       <c r="B15" t="n">
